--- a/dataset_t6_grouped/results2/G3/G3_T7503_W0058F0003T0006Z000C1N97_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G3/G3_T7503_W0058F0003T0006Z000C1N97_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>30.32246612760025</v>
+        <v>4.92740074573504</v>
       </c>
       <c r="D2" t="n">
-        <v>29.66100804861879</v>
+        <v>4.819913807900553</v>
       </c>
       <c r="E2" t="n">
-        <v>15.56037686540644</v>
+        <v>2.528561240628547</v>
       </c>
       <c r="F2" t="n">
-        <v>14.45184274325943</v>
+        <v>2.348424445779657</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>47.30070878913246</v>
+        <v>7.686365178234024</v>
       </c>
       <c r="D3" t="n">
-        <v>46.1003142527771</v>
+        <v>7.49130106607628</v>
       </c>
       <c r="E3" t="n">
-        <v>15.56037686540644</v>
+        <v>2.528561240628547</v>
       </c>
       <c r="F3" t="n">
-        <v>14.45184274325943</v>
+        <v>2.348424445779657</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>45.19500968863163</v>
+        <v>7.34418907440264</v>
       </c>
       <c r="D4" t="n">
-        <v>14.78832121792208</v>
+        <v>2.403102197912339</v>
       </c>
       <c r="E4" t="n">
-        <v>15.56037686540644</v>
+        <v>2.528561240628547</v>
       </c>
       <c r="F4" t="n">
-        <v>14.45184274325943</v>
+        <v>2.348424445779657</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>8.336622704308889</v>
+        <v>1.354701189450195</v>
       </c>
       <c r="D5" t="n">
-        <v>8.742022642200935</v>
+        <v>1.420578679357652</v>
       </c>
       <c r="E5" t="n">
-        <v>15.56037686540644</v>
+        <v>2.528561240628547</v>
       </c>
       <c r="F5" t="n">
-        <v>14.45184274325943</v>
+        <v>2.348424445779657</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
